--- a/artfynd/A 12752-2024 artfynd.xlsx
+++ b/artfynd/A 12752-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117566952</v>
+        <v>117566978</v>
       </c>
       <c r="B8" t="n">
-        <v>90841</v>
+        <v>97857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451898</v>
+        <v>452358</v>
       </c>
       <c r="R8" t="n">
-        <v>6991478</v>
+        <v>6991108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566978</v>
+        <v>117566952</v>
       </c>
       <c r="B9" t="n">
-        <v>97857</v>
+        <v>90841</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452358</v>
+        <v>451898</v>
       </c>
       <c r="R9" t="n">
-        <v>6991108</v>
+        <v>6991478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117566971</v>
+        <v>117566969</v>
       </c>
       <c r="B13" t="n">
-        <v>97857</v>
+        <v>57287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451977</v>
+        <v>452089</v>
       </c>
       <c r="R13" t="n">
-        <v>6991644</v>
+        <v>6991482</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117566969</v>
+        <v>117566971</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452089</v>
+        <v>451977</v>
       </c>
       <c r="R14" t="n">
-        <v>6991482</v>
+        <v>6991644</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117566990</v>
+        <v>117566975</v>
       </c>
       <c r="B18" t="n">
-        <v>97753</v>
+        <v>97857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452294</v>
+        <v>452295</v>
       </c>
       <c r="R18" t="n">
-        <v>6991203</v>
+        <v>6991205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,7 +2406,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2425,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117566975</v>
+        <v>117566974</v>
       </c>
       <c r="B19" t="n">
         <v>97857</v>
@@ -2465,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452295</v>
+        <v>452136</v>
       </c>
       <c r="R19" t="n">
-        <v>6991205</v>
+        <v>6991325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117566974</v>
+        <v>117566990</v>
       </c>
       <c r="B20" t="n">
-        <v>97857</v>
+        <v>97753</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452136</v>
+        <v>452294</v>
       </c>
       <c r="R20" t="n">
-        <v>6991325</v>
+        <v>6991203</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,6 +2610,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12752-2024 artfynd.xlsx
+++ b/artfynd/A 12752-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117566973</v>
+        <v>117566957</v>
       </c>
       <c r="B2" t="n">
-        <v>97857</v>
+        <v>90499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452053</v>
+        <v>451898</v>
       </c>
       <c r="R2" t="n">
-        <v>6991428</v>
+        <v>6991478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117566984</v>
+        <v>117566975</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>97857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452130</v>
+        <v>452295</v>
       </c>
       <c r="R3" t="n">
-        <v>6991387</v>
+        <v>6991205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117566986</v>
+        <v>117566955</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>90499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452172</v>
+        <v>452020</v>
       </c>
       <c r="R4" t="n">
-        <v>6991287</v>
+        <v>6991343</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117566954</v>
+        <v>117566988</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452072</v>
+        <v>452068</v>
       </c>
       <c r="R5" t="n">
-        <v>6991303</v>
+        <v>6991415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117566955</v>
+        <v>117566987</v>
       </c>
       <c r="B6" t="n">
-        <v>90499</v>
+        <v>79561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452020</v>
+        <v>452008</v>
       </c>
       <c r="R6" t="n">
-        <v>6991343</v>
+        <v>6991361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117566977</v>
+        <v>117566964</v>
       </c>
       <c r="B7" t="n">
-        <v>97857</v>
+        <v>57287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452334</v>
+        <v>451971</v>
       </c>
       <c r="R7" t="n">
-        <v>6991140</v>
+        <v>6991644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117566978</v>
+        <v>117566986</v>
       </c>
       <c r="B8" t="n">
-        <v>97857</v>
+        <v>79561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452358</v>
+        <v>452172</v>
       </c>
       <c r="R8" t="n">
-        <v>6991108</v>
+        <v>6991287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566952</v>
+        <v>117566983</v>
       </c>
       <c r="B9" t="n">
-        <v>90841</v>
+        <v>79561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451898</v>
+        <v>452098</v>
       </c>
       <c r="R9" t="n">
-        <v>6991478</v>
+        <v>6991490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117566988</v>
+        <v>117566969</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452068</v>
+        <v>452089</v>
       </c>
       <c r="R10" t="n">
-        <v>6991415</v>
+        <v>6991482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117566964</v>
+        <v>117566989</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>97753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451971</v>
+        <v>452334</v>
       </c>
       <c r="R11" t="n">
-        <v>6991644</v>
+        <v>6991140</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117566970</v>
+        <v>117566965</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452320</v>
+        <v>451966</v>
       </c>
       <c r="R12" t="n">
-        <v>6991199</v>
+        <v>6991532</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117566969</v>
+        <v>117566954</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452089</v>
+        <v>452072</v>
       </c>
       <c r="R13" t="n">
-        <v>6991482</v>
+        <v>6991303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117566971</v>
+        <v>117566990</v>
       </c>
       <c r="B14" t="n">
-        <v>97857</v>
+        <v>97753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451977</v>
+        <v>452294</v>
       </c>
       <c r="R14" t="n">
-        <v>6991644</v>
+        <v>6991203</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1998,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2016,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117566956</v>
+        <v>117566971</v>
       </c>
       <c r="B15" t="n">
-        <v>90499</v>
+        <v>97857</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2029,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451994</v>
+        <v>451977</v>
       </c>
       <c r="R15" t="n">
-        <v>6991362</v>
+        <v>6991644</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117566989</v>
+        <v>117566974</v>
       </c>
       <c r="B16" t="n">
-        <v>97753</v>
+        <v>97857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452334</v>
+        <v>452136</v>
       </c>
       <c r="R16" t="n">
-        <v>6991140</v>
+        <v>6991325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117566985</v>
+        <v>117566956</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>90499</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2237,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452159</v>
+        <v>451994</v>
       </c>
       <c r="R17" t="n">
-        <v>6991304</v>
+        <v>6991362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117566975</v>
+        <v>117566967</v>
       </c>
       <c r="B18" t="n">
-        <v>97857</v>
+        <v>57287</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2335,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452295</v>
+        <v>452076</v>
       </c>
       <c r="R18" t="n">
-        <v>6991205</v>
+        <v>6991499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,6 +2399,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117566974</v>
+        <v>117566984</v>
       </c>
       <c r="B19" t="n">
-        <v>97857</v>
+        <v>79561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2442,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452136</v>
+        <v>452130</v>
       </c>
       <c r="R19" t="n">
-        <v>6991325</v>
+        <v>6991387</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117566990</v>
+        <v>117566985</v>
       </c>
       <c r="B20" t="n">
-        <v>97753</v>
+        <v>79561</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2544,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452294</v>
+        <v>452159</v>
       </c>
       <c r="R20" t="n">
-        <v>6991203</v>
+        <v>6991304</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2616,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117566987</v>
+        <v>117566952</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>90841</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2646,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452008</v>
+        <v>451898</v>
       </c>
       <c r="R21" t="n">
-        <v>6991361</v>
+        <v>6991478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117566983</v>
+        <v>117566977</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>97857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,25 +2748,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452098</v>
+        <v>452334</v>
       </c>
       <c r="R22" t="n">
-        <v>6991490</v>
+        <v>6991140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2838,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117566957</v>
+        <v>117566953</v>
       </c>
       <c r="B23" t="n">
         <v>90499</v>
@@ -2873,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451898</v>
+        <v>452078</v>
       </c>
       <c r="R23" t="n">
-        <v>6991478</v>
+        <v>6991288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,7 +2940,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117566967</v>
+        <v>117566970</v>
       </c>
       <c r="B24" t="n">
         <v>57287</v>
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452076</v>
+        <v>452320</v>
       </c>
       <c r="R24" t="n">
-        <v>6991499</v>
+        <v>6991199</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117566965</v>
+        <v>117566973</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3054,25 +3059,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451966</v>
+        <v>452053</v>
       </c>
       <c r="R25" t="n">
-        <v>6991532</v>
+        <v>6991428</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,11 +3123,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117566953</v>
+        <v>117566978</v>
       </c>
       <c r="B26" t="n">
-        <v>90499</v>
+        <v>97857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452078</v>
+        <v>452358</v>
       </c>
       <c r="R26" t="n">
-        <v>6991288</v>
+        <v>6991108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 12752-2024 artfynd.xlsx
+++ b/artfynd/A 12752-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117566957</v>
+        <v>117566990</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451898</v>
+        <v>452294</v>
       </c>
       <c r="R2" t="n">
-        <v>6991478</v>
+        <v>6991203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117566975</v>
+        <v>117566977</v>
       </c>
       <c r="B3" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452295</v>
+        <v>452334</v>
       </c>
       <c r="R3" t="n">
-        <v>6991205</v>
+        <v>6991140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117566955</v>
+        <v>117566987</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452020</v>
+        <v>452008</v>
       </c>
       <c r="R4" t="n">
-        <v>6991343</v>
+        <v>6991361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117566988</v>
+        <v>117566965</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452068</v>
+        <v>451966</v>
       </c>
       <c r="R5" t="n">
-        <v>6991415</v>
+        <v>6991532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117566987</v>
+        <v>117566974</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1101,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452008</v>
+        <v>452136</v>
       </c>
       <c r="R6" t="n">
-        <v>6991361</v>
+        <v>6991325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117566964</v>
+        <v>117566967</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451971</v>
+        <v>452076</v>
       </c>
       <c r="R7" t="n">
-        <v>6991644</v>
+        <v>6991499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1271,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117566986</v>
+        <v>117566955</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>90501</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452172</v>
+        <v>452020</v>
       </c>
       <c r="R8" t="n">
-        <v>6991287</v>
+        <v>6991343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566983</v>
+        <v>117566952</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>90843</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1412,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452098</v>
+        <v>451898</v>
       </c>
       <c r="R9" t="n">
-        <v>6991490</v>
+        <v>6991478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117566969</v>
+        <v>117566989</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>97755</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1514,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452089</v>
+        <v>452334</v>
       </c>
       <c r="R10" t="n">
-        <v>6991482</v>
+        <v>6991140</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1578,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117566989</v>
+        <v>117566985</v>
       </c>
       <c r="B11" t="n">
-        <v>97753</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1616,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452334</v>
+        <v>452159</v>
       </c>
       <c r="R11" t="n">
-        <v>6991140</v>
+        <v>6991304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117566965</v>
+        <v>117566971</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1718,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451966</v>
+        <v>451977</v>
       </c>
       <c r="R12" t="n">
-        <v>6991532</v>
+        <v>6991644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1782,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117566954</v>
+        <v>117566978</v>
       </c>
       <c r="B13" t="n">
-        <v>90499</v>
+        <v>97859</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452072</v>
+        <v>452358</v>
       </c>
       <c r="R13" t="n">
-        <v>6991303</v>
+        <v>6991108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117566990</v>
+        <v>117566954</v>
       </c>
       <c r="B14" t="n">
-        <v>97753</v>
+        <v>90501</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1922,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452294</v>
+        <v>452072</v>
       </c>
       <c r="R14" t="n">
-        <v>6991203</v>
+        <v>6991303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1994,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2017,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117566971</v>
+        <v>117566983</v>
       </c>
       <c r="B15" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,25 +2024,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451977</v>
+        <v>452098</v>
       </c>
       <c r="R15" t="n">
-        <v>6991644</v>
+        <v>6991490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117566974</v>
+        <v>117566956</v>
       </c>
       <c r="B16" t="n">
-        <v>97857</v>
+        <v>90501</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,25 +2126,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452136</v>
+        <v>451994</v>
       </c>
       <c r="R16" t="n">
-        <v>6991325</v>
+        <v>6991362</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,10 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117566956</v>
+        <v>117566984</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>79563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451994</v>
+        <v>452130</v>
       </c>
       <c r="R17" t="n">
-        <v>6991362</v>
+        <v>6991387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,10 +2318,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117566967</v>
+        <v>117566975</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,25 +2330,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452076</v>
+        <v>452295</v>
       </c>
       <c r="R18" t="n">
-        <v>6991499</v>
+        <v>6991205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,11 +2394,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2430,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117566984</v>
+        <v>117566970</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,21 +2436,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2470,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452130</v>
+        <v>452320</v>
       </c>
       <c r="R19" t="n">
-        <v>6991387</v>
+        <v>6991199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,6 +2496,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2532,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117566985</v>
+        <v>117566964</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452159</v>
+        <v>451971</v>
       </c>
       <c r="R20" t="n">
-        <v>6991304</v>
+        <v>6991644</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,6 +2603,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2634,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117566952</v>
+        <v>117566988</v>
       </c>
       <c r="B21" t="n">
-        <v>90841</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2646,25 +2646,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451898</v>
+        <v>452068</v>
       </c>
       <c r="R21" t="n">
-        <v>6991478</v>
+        <v>6991415</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117566977</v>
+        <v>117566986</v>
       </c>
       <c r="B22" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,25 +2748,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452334</v>
+        <v>452172</v>
       </c>
       <c r="R22" t="n">
-        <v>6991140</v>
+        <v>6991287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117566953</v>
+        <v>117566969</v>
       </c>
       <c r="B23" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452078</v>
+        <v>452089</v>
       </c>
       <c r="R23" t="n">
-        <v>6991288</v>
+        <v>6991482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2940,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117566970</v>
+        <v>117566953</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,21 +2961,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452320</v>
+        <v>452078</v>
       </c>
       <c r="R24" t="n">
-        <v>6991199</v>
+        <v>6991288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,11 +3021,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117566973</v>
+        <v>117566957</v>
       </c>
       <c r="B25" t="n">
-        <v>97857</v>
+        <v>90501</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,25 +3059,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452053</v>
+        <v>451898</v>
       </c>
       <c r="R25" t="n">
-        <v>6991428</v>
+        <v>6991478</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117566978</v>
+        <v>117566973</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452358</v>
+        <v>452053</v>
       </c>
       <c r="R26" t="n">
-        <v>6991108</v>
+        <v>6991428</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 12752-2024 artfynd.xlsx
+++ b/artfynd/A 12752-2024 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117566985</v>
+        <v>117566971</v>
       </c>
       <c r="B11" t="n">
-        <v>79563</v>
+        <v>97859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,25 +1616,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452159</v>
+        <v>451977</v>
       </c>
       <c r="R11" t="n">
-        <v>6991304</v>
+        <v>6991644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117566971</v>
+        <v>117566978</v>
       </c>
       <c r="B12" t="n">
         <v>97859</v>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451977</v>
+        <v>452358</v>
       </c>
       <c r="R12" t="n">
-        <v>6991644</v>
+        <v>6991108</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117566978</v>
+        <v>117566985</v>
       </c>
       <c r="B13" t="n">
-        <v>97859</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1820,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452358</v>
+        <v>452159</v>
       </c>
       <c r="R13" t="n">
-        <v>6991108</v>
+        <v>6991304</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
